--- a/DUC_DCC_LogAPI/Files/reportDUCSendMail.xlsx
+++ b/DUC_DCC_LogAPI/Files/reportDUCSendMail.xlsx
@@ -90,22 +90,97 @@
     <x:t>Usual Event</x:t>
   </x:si>
   <x:si>
-    <x:t>Lead Test Engineer 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACACIA-LASER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACACIA/Tunable_Laser/CMD-2159_Defect_Photo.zip</x:t>
+    <x:t>Lead Tooling Design Engineer 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acacia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/PIC_CIM8 VE.zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Download</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thanasaden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unusual Event</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lead Quality Engineer 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QA - Operation QC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/CG contamination .zip</x:t>
   </x:si>
   <x:si>
     <x:t>Upload</x:t>
   </x:si>
   <x:si>
-    <x:t>thanawatsa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACACIA</x:t>
+    <x:t>yaowalakt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/DPPM PCBA level New template 1-31 July -2025.xlsx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>somjaip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/FBN Thailand - Monthly Component DPPM 1-31 July 2025.PCBA level update.xlsx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Process Engineer 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/JAYA 100ZR Fiber Attach Photospower drop PRR1415.zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pokawinc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quality Engineer 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/Wafer_Processing/Wafer yield Issue tracker_25WW31.xlsx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>benjawant</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/Bay20.zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sajitta@cisco.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/JAYA 100ZR Fiber Attach Photospower drop PRR1415 (2).zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Assessor 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA-RMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/FBN Thailand - Monthly Component DPPM Tracking as of 1-31 Jul 25.zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>puttharak_t</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACACIA/Debug reports-Module and Supplier FA level Jul 2025..zip</x:t>
+  </x:si>
+  <x:si>
+    <x:t>wpromsar@cisco.com</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -773,7 +848,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E3" s="13">
-        <x:v>45851.8179976852</x:v>
+        <x:v>45877.3501967593</x:v>
       </x:c>
       <x:c r="F3" s="15" t="s">
         <x:v>19</x:v>
@@ -796,6 +871,470 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N3" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E4" s="13">
+        <x:v>45877.4116550926</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G4" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H4" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I4" s="15"/>
+      <x:c r="J4" s="15"/>
+      <x:c r="K4" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L4" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M4" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N4" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="14">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E5" s="13">
+        <x:v>45877.5662615741</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I5" s="15"/>
+      <x:c r="J5" s="15"/>
+      <x:c r="K5" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L5" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M5" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N5" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="14">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E6" s="13">
+        <x:v>45877.5662615741</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G6" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H6" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I6" s="15"/>
+      <x:c r="J6" s="15"/>
+      <x:c r="K6" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L6" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M6" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N6" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="14">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="13">
+        <x:v>45877.6667939815</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G7" s="15" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H7" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I7" s="15"/>
+      <x:c r="J7" s="15"/>
+      <x:c r="K7" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L7" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="14">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="13">
+        <x:v>45877.6716087963</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I8" s="15"/>
+      <x:c r="J8" s="15"/>
+      <x:c r="K8" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M8" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N8" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="14">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E9" s="13">
+        <x:v>45877.732349537</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G9" s="15"/>
+      <x:c r="H9" s="15"/>
+      <x:c r="I9" s="15"/>
+      <x:c r="J9" s="15"/>
+      <x:c r="K9" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L9" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M9" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N9" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="14">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E10" s="13">
+        <x:v>45877.7326157407</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="15"/>
+      <x:c r="H10" s="15"/>
+      <x:c r="I10" s="15"/>
+      <x:c r="J10" s="15"/>
+      <x:c r="K10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N10" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="14">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="13">
+        <x:v>45877.732662037</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="15"/>
+      <x:c r="H11" s="15"/>
+      <x:c r="I11" s="15"/>
+      <x:c r="J11" s="15"/>
+      <x:c r="K11" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N11" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="14">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="13">
+        <x:v>45877.7697222222</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I12" s="15"/>
+      <x:c r="J12" s="15"/>
+      <x:c r="K12" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N12" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="A13" s="14">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="13">
+        <x:v>45877.7782060185</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I13" s="15"/>
+      <x:c r="J13" s="15"/>
+      <x:c r="K13" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="14">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="13">
+        <x:v>45877.7782060185</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H14" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I14" s="15"/>
+      <x:c r="J14" s="15"/>
+      <x:c r="K14" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:14">
+      <x:c r="A15" s="14">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E15" s="13">
+        <x:v>45877.8092592593</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G15" s="15"/>
+      <x:c r="H15" s="15"/>
+      <x:c r="I15" s="15"/>
+      <x:c r="J15" s="15"/>
+      <x:c r="K15" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
